--- a/sheets/대금율보/검수/동백타령.xlsx
+++ b/sheets/대금율보/검수/동백타령.xlsx
@@ -6631,8 +6631,8 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
-汰‹</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="I6" s="27" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∧‹</t>
+          <t xml:space="preserve">淋∧</t>
         </is>
       </c>
       <c r="O6" s="27"/>
@@ -6703,8 +6703,7 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢)
-‹</t>
+潢)</t>
         </is>
       </c>
       <c r="E7" s="23"/>
@@ -6769,8 +6768,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -6791,8 +6789,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林フ
-‹</t>
+          <t xml:space="preserve">林フ</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -6812,8 +6809,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M8" s="24"/>

--- a/sheets/대금율보/검수/동백타령.xlsx
+++ b/sheets/대금율보/검수/동백타령.xlsx
@@ -6263,32 +6263,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7390,10 +7390,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -7535,7 +7535,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -7672,7 +7672,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -7852,7 +7852,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -8016,7 +8016,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
